--- a/Rubric.xlsx
+++ b/Rubric.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\FSU\dev5\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6E57283-83D1-406D-8CF5-1274E8FA7DF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4581CF42-ABC0-4AA9-AB57-A5CE013C34AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="7476" yWindow="2256" windowWidth="23040" windowHeight="13560" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -116,7 +116,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="107">
   <si>
     <t>Team Code Name</t>
   </si>
@@ -127,9 +127,6 @@
     <t>Team Members</t>
   </si>
   <si>
-    <t>What do you call yourselves?</t>
-  </si>
-  <si>
     <t>Game Name</t>
   </si>
   <si>
@@ -145,9 +142,6 @@
     <t>Instructors Invited To Jira (Yes/No)</t>
   </si>
   <si>
-    <t>Not Yet</t>
-  </si>
-  <si>
     <t>Not An Issue</t>
   </si>
   <si>
@@ -425,6 +419,24 @@
   </si>
   <si>
     <t>Jaycob Singnoth</t>
+  </si>
+  <si>
+    <t>Crimson Millenia</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>Monday - Variable - Sprint Planning</t>
+  </si>
+  <si>
+    <t>Tuesday - Before/After Lecture - Check-in and collaborative work</t>
+  </si>
+  <si>
+    <t>Wednesday - Variable - Check-in/Standup</t>
+  </si>
+  <si>
+    <t>Thursday - Before/After lecture - Check-in and collaborative work</t>
   </si>
 </sst>
 </file>
@@ -1924,33 +1936,33 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="29" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B2" s="28" t="s">
-        <v>3</v>
+        <v>101</v>
       </c>
       <c r="C2" s="21" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C3" s="13" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C4" s="13" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C5" s="13" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C6" s="13" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
@@ -1961,30 +1973,40 @@
     </row>
     <row r="9" spans="1:3" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="A9" s="17" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C9" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="B9" s="17" t="s">
-        <v>29</v>
-      </c>
-      <c r="C9" s="22" t="s">
-        <v>5</v>
-      </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10" s="18"/>
+      <c r="A10" s="18">
+        <v>2851</v>
+      </c>
       <c r="B10" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="C10" s="14"/>
+        <v>92</v>
+      </c>
+      <c r="C10" s="14" t="s">
+        <v>103</v>
+      </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C11" s="1"/>
+      <c r="C11" s="1" t="s">
+        <v>104</v>
+      </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C12" s="1"/>
+      <c r="C12" s="1" t="s">
+        <v>105</v>
+      </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C13" s="1"/>
+      <c r="C13" s="1" t="s">
+        <v>106</v>
+      </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C14" s="1"/>
@@ -1994,24 +2016,24 @@
     </row>
     <row r="17" spans="1:3" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="A17" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="B17" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="B17" s="17" t="s">
+      <c r="C17" s="15" t="s">
         <v>7</v>
-      </c>
-      <c r="C17" s="15" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" s="25" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B18" s="27" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C18" s="26" t="s">
-        <v>9</v>
+        <v>102</v>
       </c>
     </row>
   </sheetData>
@@ -2039,74 +2061,74 @@
   <sheetData>
     <row r="1" spans="1:7" ht="23.4" x14ac:dyDescent="0.45">
       <c r="A1" s="30" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B1" s="31" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C1" s="31" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="34" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B2" s="34"/>
       <c r="C2" s="33"/>
       <c r="E2" s="5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="12" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C3" s="4">
         <v>5</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="12" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C4" s="4">
         <v>2</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="12" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C5" s="4">
         <v>2</v>
@@ -2114,10 +2136,10 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="12" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C6" s="4">
         <v>2</v>
@@ -2125,17 +2147,17 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="34" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B7" s="34"/>
       <c r="C7" s="33"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="12" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C8" s="4">
         <v>4</v>
@@ -2143,10 +2165,10 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="12" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C9" s="4">
         <v>4</v>
@@ -2154,10 +2176,10 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="12" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C10" s="4">
         <v>3</v>
@@ -2165,10 +2187,10 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="12" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C11" s="4">
         <v>3</v>
@@ -2176,10 +2198,10 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="12" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C12" s="4">
         <v>3</v>
@@ -2187,10 +2209,10 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="12" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C13" s="4">
         <v>3</v>
@@ -2198,10 +2220,10 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="12" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C14" s="4">
         <v>2</v>
@@ -2209,10 +2231,10 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="12" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C15" s="4">
         <v>2</v>
@@ -2220,17 +2242,17 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="34" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B16" s="34"/>
       <c r="C16" s="33"/>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" s="12" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C17" s="4">
         <v>5</v>
@@ -2238,10 +2260,10 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" s="12" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C18" s="4">
         <v>4</v>
@@ -2249,10 +2271,10 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" s="12" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C19" s="4">
         <v>4</v>
@@ -2260,10 +2282,10 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" s="12" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B20" s="10" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C20" s="4">
         <v>4</v>
@@ -2271,10 +2293,10 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" s="12" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C21" s="4">
         <v>4</v>
@@ -2282,10 +2304,10 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" s="12" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B22" s="10" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C22" s="4">
         <v>4</v>
@@ -2293,10 +2315,10 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" s="12" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B23" s="10" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C23" s="4">
         <v>4</v>
@@ -2304,10 +2326,10 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" s="12" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B24" s="10" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C24" s="4">
         <v>3</v>
@@ -2315,10 +2337,10 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" s="12" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B25" s="10" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C25" s="4">
         <v>3</v>
@@ -2326,10 +2348,10 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" s="12" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B26" s="10" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C26" s="4">
         <v>3</v>
@@ -2337,10 +2359,10 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" s="12" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B27" s="10" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C27" s="4">
         <v>3</v>
@@ -2348,10 +2370,10 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" s="12" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B28" s="10" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C28" s="4">
         <v>3</v>
@@ -2359,10 +2381,10 @@
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" s="12" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B29" s="10" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C29" s="4">
         <v>2</v>
@@ -2370,17 +2392,17 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" s="34" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B30" s="34"/>
       <c r="C30" s="33"/>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" s="12" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B31" s="10" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C31" s="4">
         <v>5</v>
@@ -2388,10 +2410,10 @@
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32" s="12" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B32" s="10" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C32" s="4">
         <v>4</v>
@@ -2399,10 +2421,10 @@
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33" s="12" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B33" s="10" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C33" s="4">
         <v>2</v>
@@ -2410,17 +2432,17 @@
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34" s="34" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B34" s="34"/>
       <c r="C34" s="33"/>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35" s="12" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B35" s="10" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C35" s="4">
         <v>4</v>
@@ -2428,10 +2450,10 @@
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A36" s="12" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B36" s="10" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C36" s="4">
         <v>4</v>
@@ -2439,7 +2461,7 @@
     </row>
     <row r="37" spans="1:3" ht="23.4" x14ac:dyDescent="0.45">
       <c r="A37" s="32" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B37" s="32">
         <f>SUMPRODUCT(SUMIF($B$3:$B$36,$E$2,$C$3:$C$36))+SUMPRODUCT(SUMIF($B$3:$B$36,$E$3,$C$3:$C$36))*0.5</f>
@@ -2461,21 +2483,21 @@
     </row>
     <row r="40" spans="1:3" ht="23.4" x14ac:dyDescent="0.45">
       <c r="A40" s="36" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B40" s="37" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C40" s="39" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A41" s="11" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B41" s="10" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C41" s="8">
         <v>2</v>
@@ -2483,10 +2505,10 @@
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A42" s="11" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B42" s="10" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C42" s="8">
         <v>2</v>
@@ -2494,10 +2516,10 @@
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A43" s="11" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B43" s="10" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C43" s="8">
         <v>2</v>
@@ -2505,10 +2527,10 @@
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A44" s="11" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B44" s="10" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C44" s="8">
         <v>3</v>
@@ -2516,10 +2538,10 @@
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A45" s="11" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B45" s="10" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C45" s="8">
         <v>3</v>
@@ -2527,10 +2549,10 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A46" s="11" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B46" s="10" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C46" s="8">
         <v>3</v>
@@ -2538,7 +2560,7 @@
     </row>
     <row r="47" spans="1:3" ht="23.4" x14ac:dyDescent="0.45">
       <c r="A47" s="32" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B47" s="32">
         <f>$B$37+SUMPRODUCT(SUMIF($B$41:$B$46,$F$2,$C$41:$C$46))+SUMPRODUCT(SUMIF($B$41:$B$46,$F$3,$C$41:$C$46))*0.5</f>
@@ -2551,77 +2573,77 @@
     </row>
     <row r="50" spans="1:2" ht="23.4" x14ac:dyDescent="0.45">
       <c r="A50" s="36" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B50" s="46"/>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" s="12" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B51" s="10" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" s="12" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B52" s="10" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" s="12" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B53" s="10" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" s="12" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B54" s="10" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" s="12" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B55" s="10" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" s="12" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B56" s="10" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" s="12" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B57" s="10" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" s="12" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B58" s="10" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="59" spans="1:2" ht="23.4" x14ac:dyDescent="0.45">
       <c r="A59" s="32" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B59" s="45">
         <f>IF(COUNTIF($B$51:$B$58,$G$3), 0, $B$47)</f>
@@ -2630,146 +2652,146 @@
     </row>
     <row r="62" spans="1:2" ht="23.4" x14ac:dyDescent="0.45">
       <c r="A62" s="36" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B62" s="41" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" s="34" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B63" s="42"/>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" s="11" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B64" s="10" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="B65" s="10" t="s">
         <v>15</v>
-      </c>
-      <c r="B65" s="10" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" s="11" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B66" s="10" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" s="11" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B67" s="10" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" s="34" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B68" s="42"/>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" s="11" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B69" s="10" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" s="11" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B70" s="10" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" s="11" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B71" s="10" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" s="34" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B72" s="42"/>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" s="11" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B73" s="10" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A74" s="11" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B74" s="10" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A75" s="11" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B75" s="10" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A76" s="11" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B76" s="10" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="79" spans="1:2" ht="19.8" x14ac:dyDescent="0.4">
       <c r="A79" s="44" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B79" s="43"/>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A80" s="40" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B80" s="10" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A81" s="40" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B81" s="10" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A82" s="40" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B82" s="38" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>

--- a/Rubric.xlsx
+++ b/Rubric.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\FSU\dev5\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\xinar\source\repos\Dev5\Red-2604\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4581CF42-ABC0-4AA9-AB57-A5CE013C34AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B36E6A1-E29D-43A0-ACBF-409E20BDB0F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7476" yWindow="2256" windowWidth="23040" windowHeight="13560" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="16220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Team Info" sheetId="1" r:id="rId1"/>
@@ -1918,12 +1918,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:C18"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="3" width="50.6640625" customWidth="1"/>
+    <col min="1" max="3" width="50.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="19.8" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" ht="19.5" x14ac:dyDescent="0.45">
       <c r="A1" s="19" t="s">
         <v>0</v>
       </c>
@@ -1934,7 +1934,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="29" t="s">
         <v>95</v>
       </c>
@@ -1945,33 +1945,33 @@
         <v>96</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="C3" s="13" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="C4" s="13" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="C5" s="13" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="C6" s="13" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="C7" s="24"/>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="C8" s="23"/>
     </row>
-    <row r="9" spans="1:3" ht="17.399999999999999" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:3" ht="17" x14ac:dyDescent="0.4">
       <c r="A9" s="17" t="s">
         <v>3</v>
       </c>
@@ -1982,7 +1982,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" s="18">
         <v>2851</v>
       </c>
@@ -1993,28 +1993,28 @@
         <v>103</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="C11" s="1" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="C12" s="1" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="C13" s="1" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="C14" s="1"/>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="C15" s="1"/>
     </row>
-    <row r="17" spans="1:3" ht="17.399999999999999" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:3" ht="17" x14ac:dyDescent="0.4">
       <c r="A17" s="17" t="s">
         <v>5</v>
       </c>
@@ -2025,7 +2025,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" s="25" t="s">
         <v>93</v>
       </c>
@@ -2050,16 +2050,16 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{976D0730-B5D0-49E5-8631-8CC13B9FE765}">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:G82"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="83.44140625" customWidth="1"/>
-    <col min="2" max="3" width="18.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.109375" customWidth="1"/>
-    <col min="5" max="7" width="9.109375" hidden="1" customWidth="1"/>
-    <col min="11" max="13" width="9.109375" customWidth="1"/>
+    <col min="1" max="1" width="83.453125" customWidth="1"/>
+    <col min="2" max="3" width="18.6328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.08984375" customWidth="1"/>
+    <col min="5" max="7" width="9.08984375" hidden="1" customWidth="1"/>
+    <col min="11" max="13" width="9.08984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="23.4" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:7" ht="23.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="30" t="s">
         <v>34</v>
       </c>
@@ -2070,7 +2070,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" s="34" t="s">
         <v>74</v>
       </c>
@@ -2086,7 +2086,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" s="12" t="s">
         <v>69</v>
       </c>
@@ -2106,7 +2106,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" s="12" t="s">
         <v>72</v>
       </c>
@@ -2123,7 +2123,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" s="12" t="s">
         <v>73</v>
       </c>
@@ -2134,7 +2134,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" s="12" t="s">
         <v>80</v>
       </c>
@@ -2145,14 +2145,14 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" s="34" t="s">
         <v>83</v>
       </c>
       <c r="B7" s="34"/>
       <c r="C7" s="33"/>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" s="12" t="s">
         <v>68</v>
       </c>
@@ -2163,7 +2163,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9" s="12" t="s">
         <v>86</v>
       </c>
@@ -2174,7 +2174,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10" s="12" t="s">
         <v>85</v>
       </c>
@@ -2185,7 +2185,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11" s="12" t="s">
         <v>84</v>
       </c>
@@ -2196,7 +2196,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12" s="12" t="s">
         <v>87</v>
       </c>
@@ -2207,7 +2207,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A13" s="12" t="s">
         <v>33</v>
       </c>
@@ -2218,7 +2218,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A14" s="12" t="s">
         <v>32</v>
       </c>
@@ -2229,7 +2229,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A15" s="12" t="s">
         <v>25</v>
       </c>
@@ -2240,14 +2240,14 @@
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A16" s="34" t="s">
         <v>42</v>
       </c>
       <c r="B16" s="34"/>
       <c r="C16" s="33"/>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" s="12" t="s">
         <v>81</v>
       </c>
@@ -2258,7 +2258,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" s="12" t="s">
         <v>47</v>
       </c>
@@ -2269,7 +2269,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" s="12" t="s">
         <v>48</v>
       </c>
@@ -2280,7 +2280,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" s="12" t="s">
         <v>91</v>
       </c>
@@ -2291,7 +2291,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" s="12" t="s">
         <v>90</v>
       </c>
@@ -2302,7 +2302,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22" s="12" t="s">
         <v>43</v>
       </c>
@@ -2313,7 +2313,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23" s="12" t="s">
         <v>45</v>
       </c>
@@ -2324,7 +2324,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A24" s="12" t="s">
         <v>40</v>
       </c>
@@ -2335,7 +2335,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25" s="12" t="s">
         <v>41</v>
       </c>
@@ -2346,7 +2346,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26" s="12" t="s">
         <v>44</v>
       </c>
@@ -2357,7 +2357,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A27" s="12" t="s">
         <v>46</v>
       </c>
@@ -2368,7 +2368,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A28" s="12" t="s">
         <v>37</v>
       </c>
@@ -2379,7 +2379,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A29" s="12" t="s">
         <v>88</v>
       </c>
@@ -2390,14 +2390,14 @@
         <v>2</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A30" s="34" t="s">
         <v>65</v>
       </c>
       <c r="B30" s="34"/>
       <c r="C30" s="33"/>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A31" s="12" t="s">
         <v>70</v>
       </c>
@@ -2408,7 +2408,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A32" s="12" t="s">
         <v>76</v>
       </c>
@@ -2419,7 +2419,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A33" s="12" t="s">
         <v>75</v>
       </c>
@@ -2430,14 +2430,14 @@
         <v>2</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A34" s="34" t="s">
         <v>78</v>
       </c>
       <c r="B34" s="34"/>
       <c r="C34" s="33"/>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A35" s="12" t="s">
         <v>79</v>
       </c>
@@ -2448,7 +2448,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A36" s="12" t="s">
         <v>71</v>
       </c>
@@ -2459,7 +2459,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="37" spans="1:3" ht="23.4" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:3" ht="23.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" s="32" t="s">
         <v>39</v>
       </c>
@@ -2472,16 +2472,16 @@
         <v>100</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A38" s="3"/>
       <c r="B38" s="2"/>
       <c r="C38" s="2"/>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B39" s="2"/>
       <c r="C39" s="2"/>
     </row>
-    <row r="40" spans="1:3" ht="23.4" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:3" ht="23.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A40" s="36" t="s">
         <v>49</v>
       </c>
@@ -2492,7 +2492,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A41" s="11" t="s">
         <v>26</v>
       </c>
@@ -2503,7 +2503,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A42" s="11" t="s">
         <v>58</v>
       </c>
@@ -2514,7 +2514,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A43" s="11" t="s">
         <v>63</v>
       </c>
@@ -2525,7 +2525,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A44" s="11" t="s">
         <v>67</v>
       </c>
@@ -2536,7 +2536,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A45" s="11" t="s">
         <v>20</v>
       </c>
@@ -2547,7 +2547,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A46" s="11" t="s">
         <v>11</v>
       </c>
@@ -2558,7 +2558,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="47" spans="1:3" ht="23.4" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:3" ht="23.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A47" s="32" t="s">
         <v>61</v>
       </c>
@@ -2571,13 +2571,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:2" ht="23.4" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:2" ht="23.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A50" s="36" t="s">
         <v>62</v>
       </c>
       <c r="B50" s="46"/>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A51" s="12" t="s">
         <v>28</v>
       </c>
@@ -2585,7 +2585,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A52" s="12" t="s">
         <v>29</v>
       </c>
@@ -2593,7 +2593,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A53" s="12" t="s">
         <v>36</v>
       </c>
@@ -2601,7 +2601,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A54" s="12" t="s">
         <v>31</v>
       </c>
@@ -2609,7 +2609,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A55" s="12" t="s">
         <v>89</v>
       </c>
@@ -2617,7 +2617,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A56" s="12" t="s">
         <v>77</v>
       </c>
@@ -2625,7 +2625,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A57" s="12" t="s">
         <v>82</v>
       </c>
@@ -2633,7 +2633,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A58" s="12" t="s">
         <v>64</v>
       </c>
@@ -2641,7 +2641,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="59" spans="1:2" ht="23.4" x14ac:dyDescent="0.45">
+    <row r="59" spans="1:2" ht="23.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A59" s="32" t="s">
         <v>66</v>
       </c>
@@ -2650,7 +2650,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:2" ht="23.4" x14ac:dyDescent="0.45">
+    <row r="62" spans="1:2" ht="23.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A62" s="36" t="s">
         <v>53</v>
       </c>
@@ -2658,13 +2658,13 @@
         <v>18</v>
       </c>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A63" s="34" t="s">
         <v>51</v>
       </c>
       <c r="B63" s="42"/>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A64" s="11" t="s">
         <v>59</v>
       </c>
@@ -2672,7 +2672,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A65" s="11" t="s">
         <v>13</v>
       </c>
@@ -2680,7 +2680,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A66" s="11" t="s">
         <v>60</v>
       </c>
@@ -2688,7 +2688,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A67" s="11" t="s">
         <v>30</v>
       </c>
@@ -2696,13 +2696,13 @@
         <v>15</v>
       </c>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A68" s="34" t="s">
         <v>54</v>
       </c>
       <c r="B68" s="42"/>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A69" s="11" t="s">
         <v>55</v>
       </c>
@@ -2710,7 +2710,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A70" s="11" t="s">
         <v>56</v>
       </c>
@@ -2718,7 +2718,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A71" s="11" t="s">
         <v>19</v>
       </c>
@@ -2726,13 +2726,13 @@
         <v>15</v>
       </c>
     </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A72" s="34" t="s">
         <v>52</v>
       </c>
       <c r="B72" s="42"/>
     </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A73" s="11" t="s">
         <v>12</v>
       </c>
@@ -2740,7 +2740,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A74" s="11" t="s">
         <v>17</v>
       </c>
@@ -2748,7 +2748,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A75" s="11" t="s">
         <v>16</v>
       </c>
@@ -2756,7 +2756,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A76" s="11" t="s">
         <v>57</v>
       </c>
@@ -2764,13 +2764,13 @@
         <v>15</v>
       </c>
     </row>
-    <row r="79" spans="1:2" ht="19.8" x14ac:dyDescent="0.4">
+    <row r="79" spans="1:2" ht="19.5" x14ac:dyDescent="0.45">
       <c r="A79" s="44" t="s">
         <v>21</v>
       </c>
       <c r="B79" s="43"/>
     </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A80" s="40" t="s">
         <v>24</v>
       </c>
@@ -2778,7 +2778,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A81" s="40" t="s">
         <v>23</v>
       </c>
@@ -2786,7 +2786,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A82" s="40" t="s">
         <v>22</v>
       </c>
